--- a/docs/analysis/PACT-bundle-pricing.xlsx
+++ b/docs/analysis/PACT-bundle-pricing.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v0.347</t>
+          <t>v0.348</t>
         </is>
       </c>
     </row>
@@ -762,14 +762,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>This reproduces 20 of the 21 stored prices exactly; Circle of the Sea is the single miss (charged</t>
+          <t>As of DATA.version v0.348 this reproduces ALL 21 stored prices exactly. Circle of the Sea used to be</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>11/9 where its seven paid grants total 12/10 - the same shape as Aberrant Sorcery, charged 12/10).</t>
+          <t>the one miss - charged 11/9 where its list totals 12/10 - and was repriced to 12/10 in that version.</t>
         </is>
       </c>
     </row>
@@ -9481,10 +9481,10 @@
         <v/>
       </c>
       <c r="G8" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I8" s="8">
         <f>G8-E8</f>
